--- a/datasets/raw/school_info_2023.xlsx
+++ b/datasets/raw/school_info_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://shamiriteam-my.sharepoint.com/personal/rachael_kilonzo_shamiri_institute/Documents/Documents/Projects/Combined M&amp;E/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Racheal\Documents\MHDP\datasets\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_3A7AE175CB385EDFDA183B69E1230AEB82D8BC2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C5450B3-DD72-4DEC-8A9E-9EE3D1CE62C1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:8001_{44E7B889-A151-4C5C-937A-9FBFF283CF0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24" yWindow="48" windowWidth="11652" windowHeight="12168" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Query result" sheetId="1" r:id="rId1"/>
